--- a/data/trans_orig/IP07A11-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07A11-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido estar al aire libre en 2007 (tasa de respuesta: 99,6%)</t>
+          <t>Menores según la frecuencia de haber podido estar al aire libre, percibida por el adulto en 2007 (tasa de respuesta: 99,6%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>37400</t>
+          <t>37603</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>54605</t>
+          <t>55017</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>47204</t>
+          <t>47349</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>65764</t>
+          <t>66181</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>46,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>89669</t>
+          <t>88612</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>114525</t>
+          <t>113592</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>42,32%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48605</t>
+          <t>49674</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>66631</t>
+          <t>66538</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,51%</t>
+          <t>52,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>56946</t>
+          <t>56792</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>75484</t>
+          <t>76236</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>111327</t>
+          <t>112509</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>137905</t>
+          <t>139299</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>51,9%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14530</t>
+          <t>14923</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28780</t>
+          <t>28414</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11881</t>
+          <t>12007</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>24792</t>
+          <t>24820</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>30631</t>
+          <t>30712</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>50067</t>
+          <t>49270</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,36%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4935</t>
+          <t>4534</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4205</t>
+          <t>2819</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>653</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6236</t>
+          <t>5611</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2319</t>
+          <t>2176</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2528</t>
+          <t>2680</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>52901</t>
+          <t>54746</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>75411</t>
+          <t>75696</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>70561</t>
+          <t>71813</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>92835</t>
+          <t>92855</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>131790</t>
+          <t>130170</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>161304</t>
+          <t>160962</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>40,43%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>86293</t>
+          <t>86342</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>109153</t>
+          <t>107135</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>55,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>81160</t>
+          <t>81971</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>104635</t>
+          <t>104445</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>174947</t>
+          <t>175210</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>205991</t>
+          <t>205976</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>44,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22096</t>
+          <t>22572</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>39169</t>
+          <t>39227</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18389</t>
+          <t>19040</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>33841</t>
+          <t>34189</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>44614</t>
+          <t>44977</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>67718</t>
+          <t>66159</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,62%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1158</t>
+          <t>789</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7151</t>
+          <t>7123</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>615</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6009</t>
+          <t>5816</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2493</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10086</t>
+          <t>9833</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4091</t>
+          <t>4455</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4086</t>
+          <t>3218</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>95083</t>
+          <t>96092</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>122243</t>
+          <t>124437</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>123782</t>
+          <t>125182</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>153070</t>
+          <t>154451</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>228089</t>
+          <t>226530</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>267934</t>
+          <t>268509</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>40,28%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>141799</t>
+          <t>141077</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>170559</t>
+          <t>170483</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>53,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>145222</t>
+          <t>144566</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>173807</t>
+          <t>173229</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>50,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>293619</t>
+          <t>296817</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>335958</t>
+          <t>339033</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>50,86%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>41181</t>
+          <t>40593</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>62311</t>
+          <t>62198</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>33877</t>
+          <t>34187</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>53772</t>
+          <t>54347</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>81324</t>
+          <t>79959</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>109493</t>
+          <t>108915</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,34%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1376</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8482</t>
+          <t>8497</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>1175</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7125</t>
+          <t>7321</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3929</t>
+          <t>3874</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12994</t>
+          <t>12982</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2608</t>
+          <t>2323</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3388</t>
+          <t>3409</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4127</t>
+          <t>4296</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -2813,7 +2813,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido estar al aire libre en 2012 (tasa de respuesta: 98,23%)</t>
+          <t>Menores según la frecuencia de haber podido estar al aire libre, percibida por el adulto en 2012 (tasa de respuesta: 98,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>78935</t>
+          <t>79552</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>100209</t>
+          <t>100154</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,76%</t>
+          <t>51,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>64,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>68262</t>
+          <t>67074</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>87216</t>
+          <t>88070</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>56,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>153539</t>
+          <t>151918</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>183043</t>
+          <t>181871</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>48,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>58,26%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47636</t>
+          <t>46776</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>67844</t>
+          <t>66591</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>54337</t>
+          <t>53520</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>73498</t>
+          <t>73817</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,91%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>106348</t>
+          <t>105898</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>134489</t>
+          <t>135080</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>43,27%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4755</t>
+          <t>4471</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14195</t>
+          <t>14213</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9010</t>
+          <t>8743</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21131</t>
+          <t>20909</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>15653</t>
+          <t>15795</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>31751</t>
+          <t>31060</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>9,95%</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3541</t>
+          <t>3184</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4578</t>
+          <t>5108</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>619</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5189</t>
+          <t>5131</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>72389</t>
+          <t>72280</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>94400</t>
+          <t>93992</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>43,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>56,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>90537</t>
+          <t>92709</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>112795</t>
+          <t>112816</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>52,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,15%</t>
+          <t>64,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>171741</t>
+          <t>172036</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>201272</t>
+          <t>200512</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>50,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>58,46%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>56450</t>
+          <t>55910</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>77099</t>
+          <t>76001</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>50754</t>
+          <t>51487</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>71234</t>
+          <t>71032</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>111360</t>
+          <t>112179</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>140337</t>
+          <t>140732</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>41,03%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10510</t>
+          <t>11227</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23759</t>
+          <t>23949</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4805</t>
+          <t>4344</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13765</t>
+          <t>13418</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>18295</t>
+          <t>18408</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>34044</t>
+          <t>34061</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -4034,7 +4034,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4805</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4064,12 +4064,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>1201</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8146</t>
+          <t>7272</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4079,12 +4079,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9954</t>
+          <t>9268</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -4182,7 +4182,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4843</t>
+          <t>4565</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4563</t>
+          <t>4499</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>158844</t>
+          <t>157065</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>187235</t>
+          <t>186000</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>48,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>57,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>166008</t>
+          <t>165792</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>195146</t>
+          <t>194485</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>58,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>332317</t>
+          <t>333438</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>373725</t>
+          <t>374374</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>57,14%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>107480</t>
+          <t>109631</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>137045</t>
+          <t>137987</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>109603</t>
+          <t>110293</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>138011</t>
+          <t>139073</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>225573</t>
+          <t>226943</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>265749</t>
+          <t>266584</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>40,69%</t>
         </is>
       </c>
     </row>
@@ -4598,12 +4598,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17927</t>
+          <t>18132</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>34330</t>
+          <t>33911</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4613,12 +4613,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4633,12 +4633,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>15027</t>
+          <t>15609</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>30848</t>
+          <t>30594</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>37671</t>
+          <t>36600</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>59562</t>
+          <t>58208</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,88%</t>
         </is>
       </c>
     </row>
@@ -4711,12 +4711,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>626</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5727</t>
+          <t>5823</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4746,12 +4746,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>1854</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8703</t>
+          <t>8633</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3472</t>
+          <t>3121</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11905</t>
+          <t>11374</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4513</t>
+          <t>4674</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4033</t>
+          <t>4194</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5089,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido estar al aire libre en 2016 (tasa de respuesta: 98,92%)</t>
+          <t>Menores según la frecuencia de haber podido estar al aire libre, percibida por el adulto en 2016 (tasa de respuesta: 98,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5284,12 +5284,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>85884</t>
+          <t>85294</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>109003</t>
+          <t>108619</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5299,12 +5299,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>58,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5319,12 +5319,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>92256</t>
+          <t>91193</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>113977</t>
+          <t>114474</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>48,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>61,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>185225</t>
+          <t>184246</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>216072</t>
+          <t>215583</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>49,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>57,75%</t>
         </is>
       </c>
     </row>
@@ -5397,12 +5397,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49551</t>
+          <t>49103</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>70363</t>
+          <t>69902</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5412,12 +5412,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5432,12 +5432,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55955</t>
+          <t>56622</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>77928</t>
+          <t>78237</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>111198</t>
+          <t>111843</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>141581</t>
+          <t>141173</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>37,82%</t>
         </is>
       </c>
     </row>
@@ -5510,12 +5510,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16133</t>
+          <t>16680</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31438</t>
+          <t>32145</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8732</t>
+          <t>9495</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21356</t>
+          <t>21604</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>27615</t>
+          <t>28894</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>47104</t>
+          <t>48691</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>13,04%</t>
         </is>
       </c>
     </row>
@@ -5623,12 +5623,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2176</t>
+          <t>2052</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9602</t>
+          <t>9860</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5638,12 +5638,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4881</t>
+          <t>5064</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3208</t>
+          <t>2910</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11731</t>
+          <t>11953</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -5741,7 +5741,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5918</t>
+          <t>6028</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5776,7 +5776,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>4407</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>1068</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7254</t>
+          <t>7688</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>68050</t>
+          <t>66823</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>90128</t>
+          <t>88403</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>51,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>73153</t>
+          <t>72819</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>96182</t>
+          <t>95545</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>41,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>145969</t>
+          <t>145823</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>178332</t>
+          <t>178169</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,81%</t>
+          <t>51,76%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>57519</t>
+          <t>57629</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>78572</t>
+          <t>78898</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>59346</t>
+          <t>61124</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>82355</t>
+          <t>81813</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>122243</t>
+          <t>123254</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>153628</t>
+          <t>154348</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,63%</t>
+          <t>44,84%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16284</t>
+          <t>15844</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>31946</t>
+          <t>30249</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10325</t>
+          <t>10769</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>23812</t>
+          <t>23591</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>29894</t>
+          <t>30056</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>49834</t>
+          <t>49278</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,32%</t>
         </is>
       </c>
     </row>
@@ -6310,7 +6310,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6106</t>
+          <t>5935</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6340,12 +6340,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>689</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7362</t>
+          <t>6768</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1397</t>
+          <t>1674</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8979</t>
+          <t>8935</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6390,12 +6390,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>158193</t>
+          <t>160545</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>189781</t>
+          <t>190763</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>170950</t>
+          <t>173250</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>204750</t>
+          <t>202594</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>47,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,66%</t>
+          <t>56,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>341192</t>
+          <t>340281</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>382552</t>
+          <t>384763</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>53,62%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>112452</t>
+          <t>113727</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>142691</t>
+          <t>143683</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>122087</t>
+          <t>122059</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>152413</t>
+          <t>151755</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6811,47 +6811,47 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
+          <t>33,78%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>42,0%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>369</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>264724</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>242439</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>285390</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>36,89%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
           <t>33,79%</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>42,18%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>369</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>264724</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>243973</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>285832</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>36,89%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>34,0%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>39,77%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>36812</t>
+          <t>36606</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>56644</t>
+          <t>57601</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>23467</t>
+          <t>21977</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40467</t>
+          <t>39776</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>63395</t>
+          <t>62416</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>90630</t>
+          <t>91134</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,7%</t>
         </is>
       </c>
     </row>
@@ -6987,12 +6987,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>3345</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12027</t>
+          <t>12156</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1451</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8404</t>
+          <t>8908</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7037,12 +7037,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5869</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16343</t>
+          <t>17096</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7072,12 +7072,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -7105,7 +7105,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5466</t>
+          <t>5723</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7120,7 +7120,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7140,7 +7140,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4336</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>748</t>
+          <t>692</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7634</t>
+          <t>7901</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7190,7 +7190,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP07A11-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07A11-Edad-trans_orig.xlsx
@@ -537,13 +537,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de haber podido estar al aire libre, percibida por el adulto en 2007 (tasa de respuesta: 99,6%)</t>
+          <t>Menores según la frecuencia de haber podido estar al aire libre, percibida por el/la adulto/a [KIDSCREEN 20] en 2007 (tasa de respuesta: 99,6%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>56200</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>47458</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>65742</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>39,71%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>33,54%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>46,46%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>45302</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>37603</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>55017</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>36642</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>54362</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>35,7%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>29,63%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>43,36%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>56200</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>47349</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>66181</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>39,71%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>88612</t>
+          <t>89423</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>113592</t>
+          <t>114380</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>42,61%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>66813</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>57099</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>76041</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>47,21%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>40,35%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>53,73%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>58621</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>49674</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>66538</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>49421</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>67740</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>46,2%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>39,15%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>52,44%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>66813</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>56792</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>76236</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>47,21%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>53,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>112509</t>
+          <t>111627</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>139299</t>
+          <t>136969</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>51,03%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>17808</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>12129</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>24789</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>12,58%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>8,57%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>17,52%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>21122</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>14923</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>28414</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>14789</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>28705</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>16,65%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>11,76%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>22,39%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>17808</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>12007</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>24820</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>12,58%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>30712</t>
+          <t>30228</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>49270</t>
+          <t>48525</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,08%</t>
         </is>
       </c>
     </row>
@@ -1061,72 +1061,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4195</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,96%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1387</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4534</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4892</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,09%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,57%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2819</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5611</t>
+          <t>5599</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1174,107 +1174,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>462</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2176</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>2352</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,36%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>1,85%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>462</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>2197</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>462</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>2680</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -1287,57 +1287,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>126894</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>126894</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>126894</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>82069</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>71697</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>93780</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>40,22%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>35,13%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>45,95%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>64034</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>54746</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>75696</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>52512</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>74588</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>32,99%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>28,21%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>39,0%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>82069</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>71813</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>92855</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>40,22%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>130170</t>
+          <t>130707</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>160962</t>
+          <t>161850</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>40,65%</t>
         </is>
       </c>
     </row>
@@ -1517,72 +1517,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>92983</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>81429</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>103973</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>45,56%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>39,9%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>50,95%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>143</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>97318</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>86342</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>107135</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>86125</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>108989</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>50,14%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>44,48%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>55,2%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>92983</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>81971</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>104445</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>45,56%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,18%</t>
+          <t>56,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>175210</t>
+          <t>173601</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>205976</t>
+          <t>206140</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>51,77%</t>
         </is>
       </c>
     </row>
@@ -1630,72 +1630,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>25850</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>19074</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>34153</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>12,67%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>9,35%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>16,74%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>29910</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>22572</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>39227</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>22943</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>39092</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>15,41%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>11,63%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>20,21%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>25850</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>19040</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>34189</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>12,67%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>44977</t>
+          <t>44719</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>66159</t>
+          <t>69046</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>17,34%</t>
         </is>
       </c>
     </row>
@@ -1748,67 +1748,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>2491</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>714</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6084</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,22%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,98%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>2834</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>789</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>7123</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>787</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6662</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,46%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,41%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,67%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2491</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>615</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5816</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,22%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9833</t>
+          <t>9785</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -1856,107 +1856,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3423</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>680</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>4455</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>4461</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>2,18%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>680</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>3218</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -1969,57 +1969,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>204072</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>204072</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>204072</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>286</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>204072</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>204072</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>204072</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2086,72 +2086,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>138268</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>122846</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>153392</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>40,01%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>35,55%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>44,39%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>164</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>109337</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>96092</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>124437</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>96937</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>123816</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>34,06%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>29,94%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>38,77%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>138268</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>125182</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>154451</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>40,01%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>226530</t>
+          <t>225917</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>268509</t>
+          <t>267599</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>40,15%</t>
         </is>
       </c>
     </row>
@@ -2199,72 +2199,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>159796</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>144280</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>175230</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>46,24%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>41,75%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>50,71%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>155939</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>141077</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>170483</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>141454</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>169372</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>48,58%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>43,95%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>53,11%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>159796</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>144566</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>173229</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>46,24%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>44,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>52,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>296817</t>
+          <t>295525</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>339033</t>
+          <t>338524</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>44,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>50,79%</t>
         </is>
       </c>
     </row>
@@ -2312,72 +2312,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>43658</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>34941</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>54848</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>12,63%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>10,11%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>15,87%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>51032</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>40593</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>62198</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>41336</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>62604</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>15,9%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>12,65%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>19,38%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>43658</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>34187</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>54347</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>12,63%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>79959</t>
+          <t>81457</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>108915</t>
+          <t>111532</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,73%</t>
         </is>
       </c>
     </row>
@@ -2425,72 +2425,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>3186</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1096</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>6595</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1,91%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>4221</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>1949</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>8497</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>1486</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>8913</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>1,32%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>2,65%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>3186</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>1175</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>7321</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3874</t>
+          <t>3646</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12982</t>
+          <t>12422</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -2543,102 +2543,102 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>3635</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
           <t>462</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2323</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>2327</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,14%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>680</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>3409</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>4403</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>4296</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -2651,57 +2651,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>519</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>345587</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>345587</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>345587</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>476</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>320991</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>320991</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>320991</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>345587</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>345587</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>345587</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2813,13 +2813,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de haber podido estar al aire libre, percibida por el adulto en 2012 (tasa de respuesta: 98,23%)</t>
+          <t>Menores según la frecuencia de haber podido estar al aire libre, percibida por el/la adulto/a [KIDSCREEN 20] en 2012 (tasa de respuesta: 98,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2830,7 +2830,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2998,72 +2998,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>77665</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>68597</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>89194</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>49,57%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>43,78%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>56,93%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>89723</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>79552</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>100154</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>79581</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>99957</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>57,69%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>51,15%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>64,4%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>77665</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>67074</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>88070</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>49,57%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>51,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
+          <t>64,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>151918</t>
+          <t>152744</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>181871</t>
+          <t>180755</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>48,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>57,9%</t>
         </is>
       </c>
     </row>
@@ -3111,72 +3111,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>63621</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>52839</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>73183</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>40,61%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>33,73%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>46,71%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>56738</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>46776</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>66591</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>47199</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>67431</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>36,48%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>30,08%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>42,82%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>63621</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>53520</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>73817</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>40,61%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>105898</t>
+          <t>107243</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>135080</t>
+          <t>134126</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>42,96%</t>
         </is>
       </c>
     </row>
@@ -3224,72 +3224,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>14085</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>8922</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>21218</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>8,99%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>5,69%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>13,54%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>8426</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>4471</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>14213</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>4327</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>14147</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>5,42%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,88%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>9,14%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>14085</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>8743</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>20909</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>8,99%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>15795</t>
+          <t>15963</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>31060</t>
+          <t>31835</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,2%</t>
         </is>
       </c>
     </row>
@@ -3337,72 +3337,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1304</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4498</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,87%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>627</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3184</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3356</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,4%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,05%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1304</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5108</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>622</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>5789</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -3563,57 +3563,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>156674</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>156674</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>156674</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>221</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>155514</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>155514</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>155514</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>156674</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>156674</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>156674</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3680,72 +3680,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>103079</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>91582</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>113411</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>58,62%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>52,08%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>64,5%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>83048</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>72280</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>93992</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>73253</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>95030</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>49,69%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>43,25%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>56,24%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>103079</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>92709</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>112816</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>58,62%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>172036</t>
+          <t>171160</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>200512</t>
+          <t>201987</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>49,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>58,89%</t>
         </is>
       </c>
     </row>
@@ -3793,72 +3793,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>60112</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>50225</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>71165</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>34,19%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>28,56%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>40,47%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>65908</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>55910</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>76001</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>54253</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>75660</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>39,44%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>33,45%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>45,47%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>60112</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>51487</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>71032</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>34,19%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>112179</t>
+          <t>111272</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>140732</t>
+          <t>139329</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>40,62%</t>
         </is>
       </c>
     </row>
@@ -3906,72 +3906,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>8149</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>4565</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>13262</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>4,63%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>7,54%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>16710</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>11227</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>23949</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>10835</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>24289</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>10,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>6,72%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>14,33%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>8149</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>4344</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>13418</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>4,63%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>18408</t>
+          <t>17786</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>34061</t>
+          <t>33817</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,86%</t>
         </is>
       </c>
     </row>
@@ -4019,72 +4019,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1231</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7407</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,21%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1464</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5323</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5111</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,88%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,18%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3201</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1201</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>7272</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9268</t>
+          <t>9105</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -4132,107 +4132,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1294</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4612</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2,62%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>1294</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>4565</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>5169</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>2,6%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1294</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>4499</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -4245,57 +4245,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>175834</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>175834</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>175834</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>237</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>167130</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>167130</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>167130</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>259</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>175834</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>175834</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>175834</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4362,72 +4362,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>180743</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>165220</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>195602</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>54,36%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>49,69%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>58,83%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>172772</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>157065</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>186000</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>158240</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>187476</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>53,55%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>48,68%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>57,65%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>180743</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>165792</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>194485</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>54,36%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>49,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>58,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>333438</t>
+          <t>332881</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>374374</t>
+          <t>374876</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>57,22%</t>
         </is>
       </c>
     </row>
@@ -4475,72 +4475,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>123732</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>109802</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>139276</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>37,21%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>33,02%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>41,89%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>175</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>122647</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>109631</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>137987</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>108286</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>136438</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>38,01%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>33,98%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>42,77%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>123732</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>110293</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>139073</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>37,21%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>226943</t>
+          <t>225632</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>266584</t>
+          <t>266035</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,61%</t>
         </is>
       </c>
     </row>
@@ -4588,72 +4588,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>22234</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>15572</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>30980</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>6,69%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>4,68%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>9,32%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>25136</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>18132</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>33911</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>17671</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>34223</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>7,79%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>5,62%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>10,51%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>22234</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>15609</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>30594</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>6,69%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>36600</t>
+          <t>37760</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>58208</t>
+          <t>59405</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,07%</t>
         </is>
       </c>
     </row>
@@ -4701,107 +4701,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>4504</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1867</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>8851</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>2,66%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>2090</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>626</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>5823</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5683</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,65%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>6595</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>3265</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>11777</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>1,01%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
         <is>
           <t>1,8%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>4504</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>1854</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>8633</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>2,6%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>6595</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>3121</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>11374</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>1,01%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -4814,107 +4814,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1294</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>4628</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>1294</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>4674</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>5186</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>1294</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>4194</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -4927,57 +4927,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>484</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>332508</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>332508</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>332508</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>458</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>322645</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>322645</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>322645</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>484</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>332508</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>332508</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>332508</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5089,13 +5089,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de haber podido estar al aire libre, percibida por el adulto en 2016 (tasa de respuesta: 98,92%)</t>
+          <t>Menores según la frecuencia de haber podido estar al aire libre, percibida por el/la adulto/a [KIDSCREEN 20] en 2016 (tasa de respuesta: 98,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5106,7 +5106,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5274,72 +5274,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>103417</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>91942</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>115277</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>55,21%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>49,08%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>61,54%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>97114</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>85294</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>108619</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>86212</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>109061</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>52,22%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>45,86%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>58,4%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>103417</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>91193</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>114474</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>55,21%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>184246</t>
+          <t>183549</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>215583</t>
+          <t>215100</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>49,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>57,62%</t>
         </is>
       </c>
     </row>
@@ -5387,72 +5387,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>66775</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>55756</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>77025</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>35,65%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>29,77%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>41,12%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>59367</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>49103</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>69902</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>48626</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>69800</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>31,92%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>26,4%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>37,58%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>66775</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>56622</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>78237</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>35,65%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,77%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>111843</t>
+          <t>111009</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>141173</t>
+          <t>140905</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,75%</t>
         </is>
       </c>
     </row>
@@ -5500,72 +5500,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>14448</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>9296</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>21791</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>7,71%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>4,96%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>11,63%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>22892</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>16680</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>32145</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>16641</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>31561</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>12,31%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>8,97%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>17,28%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>14448</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>9495</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>21604</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>7,71%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>28894</t>
+          <t>28751</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>48691</t>
+          <t>47622</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,76%</t>
         </is>
       </c>
     </row>
@@ -5613,72 +5613,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1434</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4584</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,45%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>4926</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2052</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>9860</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2033</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>9312</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,65%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5,3%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1434</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5064</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2910</t>
+          <t>2836</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11953</t>
+          <t>11319</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -5731,67 +5731,67 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>1239</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4150</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2,22%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>1684</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>6028</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>6114</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,91%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,24%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1239</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>4407</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1068</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7688</t>
+          <t>7267</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -5839,57 +5839,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>187313</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>187313</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>187313</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>267</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>185983</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>185983</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>185983</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>187313</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>187313</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>187313</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5956,72 +5956,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>84497</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>73659</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>95802</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>48,55%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>42,32%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>55,04%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>77661</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>66823</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>88403</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>66565</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>87899</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>45,64%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>39,27%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>51,95%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>84497</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>72819</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>95545</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>48,55%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>51,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>145823</t>
+          <t>147383</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>178169</t>
+          <t>177270</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>51,5%</t>
         </is>
       </c>
     </row>
@@ -6069,72 +6069,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>70508</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>59542</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>81905</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>40,51%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>34,21%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>47,06%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>68074</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>57629</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>78898</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>58097</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>79477</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>40,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>33,87%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>46,36%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>70508</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>61124</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>81813</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>40,51%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>46,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>123254</t>
+          <t>122410</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>154348</t>
+          <t>154381</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>44,85%</t>
         </is>
       </c>
     </row>
@@ -6182,72 +6182,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>16310</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>10454</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>23355</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>9,37%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>6,01%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>13,42%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>22827</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>15844</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>30249</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>31084</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>13,41%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>9,31%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>17,78%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>16310</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>10769</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>23591</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>9,37%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>30056</t>
+          <t>28837</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>49278</t>
+          <t>49269</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,31%</t>
         </is>
       </c>
     </row>
@@ -6295,74 +6295,74 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2733</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6762</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,89%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1610</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5935</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5936</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,95%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>3,49%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2733</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>689</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>6768</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>3,89%</t>
-        </is>
-      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>6</t>
@@ -6375,12 +6375,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1674</t>
+          <t>1418</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8935</t>
+          <t>9323</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6390,12 +6390,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -6521,57 +6521,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>242</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>170172</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>170172</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>170172</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6638,72 +6638,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>187914</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>170712</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>204290</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>52,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>47,24%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>56,53%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>252</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>174776</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>160545</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>190763</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>159579</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>189768</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>49,07%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>45,08%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>53,56%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>187914</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>173250</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>202594</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>52,0%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>44,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>53,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>340281</t>
+          <t>339626</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>384763</t>
+          <t>384035</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>53,52%</t>
         </is>
       </c>
     </row>
@@ -6751,72 +6751,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>137283</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>121414</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>153585</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>37,99%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>33,6%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>42,5%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>181</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>127441</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>113727</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>143683</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>112862</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>142606</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>35,78%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>31,93%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>40,34%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>137283</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>122059</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>151755</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>37,99%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>242439</t>
+          <t>244053</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>285390</t>
+          <t>285621</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>39,81%</t>
         </is>
       </c>
     </row>
@@ -6864,72 +6864,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>30759</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>22339</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>39470</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>8,51%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>6,18%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>10,92%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>45719</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>36606</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>57601</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>35520</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>56100</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>12,84%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>10,28%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>16,17%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>30759</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>21977</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>39776</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>8,51%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>62416</t>
+          <t>63062</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>91134</t>
+          <t>90575</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,62%</t>
         </is>
       </c>
     </row>
@@ -6977,72 +6977,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>4167</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1395</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>8456</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>2,34%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>6536</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>3345</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>12156</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>3125</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>12165</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>1,84%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>3,41%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>4167</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>1513</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>8908</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>5701</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17096</t>
+          <t>17308</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7072,12 +7072,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -7095,67 +7095,67 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>1239</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>4361</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1,21%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
           <t>1684</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>5723</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>7203</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,47%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>1239</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>4336</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>693</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7901</t>
+          <t>7186</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7190,7 +7190,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -7203,57 +7203,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>496</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>361361</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>361361</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>361361</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>356155</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>356155</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>356155</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>496</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>361361</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>361361</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>361361</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
